--- a/data_new/newEmployees.xlsx
+++ b/data_new/newEmployees.xlsx
@@ -22,16 +22,13 @@
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="167" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -50,21 +47,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -432,61 +420,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>EmployeeID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>FName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>LName</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SkillsTraining</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SalesmanshipTraining</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ProductTraining</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>DOB</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>StartDate</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>TerminationDate</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>LocationID</t>
         </is>
@@ -498,21 +486,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Ashley</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wu</t>
+          <t>Fletcher</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -520,11 +508,11 @@
       <c r="G2" t="b">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>30441</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>44565</v>
+      <c r="H2" s="1" t="n">
+        <v>37096</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>44564</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
@@ -539,33 +527,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Roy</t>
+          <t>Beck</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>33690</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>44562</v>
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>38155</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>44563</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
@@ -580,32 +568,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Wagner</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>36970</v>
-      </c>
-      <c r="I4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>34984</v>
+      </c>
+      <c r="I4" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -621,12 +609,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Gomez</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -635,7 +623,7 @@
         </is>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -643,11 +631,11 @@
       <c r="G5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>32978</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>44564</v>
+      <c r="H5" s="1" t="n">
+        <v>30944</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>44562</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
@@ -662,32 +650,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Glenn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cortez</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>27735</v>
-      </c>
-      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>38024</v>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -703,12 +691,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Corey</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gomez</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -717,19 +705,19 @@
         </is>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>32483</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>44929</v>
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>35659</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>44930</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
@@ -744,17 +732,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Carroll</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -764,13 +752,13 @@
         <v>0</v>
       </c>
       <c r="G8" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>27973</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>44927</v>
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>31145</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>44930</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
@@ -785,12 +773,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mccoy</t>
+          <t>Perez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -805,13 +793,13 @@
         <v>1</v>
       </c>
       <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>32787</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>44928</v>
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>31440</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>44930</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
@@ -826,21 +814,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -848,10 +836,10 @@
       <c r="G10" t="b">
         <v>1</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>31078</v>
-      </c>
-      <c r="I10" s="3" t="n">
+      <c r="H10" s="1" t="n">
+        <v>29458</v>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>44928</v>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -867,17 +855,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kimberly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -887,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>36103</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>44929</v>
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>34252</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>44927</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
@@ -908,33 +896,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Chase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Frost</t>
+          <t>Fuller</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
       </c>
       <c r="G12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>34072</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>45293</v>
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>37119</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>45294</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
@@ -949,12 +937,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aimee</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mendez</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -969,12 +957,12 @@
         <v>0</v>
       </c>
       <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>34911</v>
-      </c>
-      <c r="I13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>35404</v>
+      </c>
+      <c r="I13" s="2" t="n">
         <v>45293</v>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -990,21 +978,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ricky</t>
+          <t>Bryan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sosa</t>
+          <t>Guzman</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -1012,11 +1000,11 @@
       <c r="G14" t="b">
         <v>0</v>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>32550</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>45293</v>
+      <c r="H14" s="1" t="n">
+        <v>29629</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>45295</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
@@ -1031,33 +1019,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dennis</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Contreras</t>
+          <t>Evans</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>32891</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>45293</v>
+        <v>1</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>36954</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>45294</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
@@ -1072,12 +1060,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Eddie</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norris</t>
+          <t>Grimes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1086,19 +1074,19 @@
         </is>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
       <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>29789</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>45293</v>
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>38208</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>45292</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
@@ -1113,32 +1101,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kayla</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lewis</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
       </c>
-      <c r="H17" s="2" t="n">
-        <v>27788</v>
-      </c>
-      <c r="I17" s="3" t="n">
+      <c r="H17" s="1" t="n">
+        <v>29299</v>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1154,33 +1142,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Nathaniel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wheeler</t>
+          <t>Gordon</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>35683</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>45659</v>
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>35791</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>45660</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
@@ -1195,33 +1183,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sonya</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palmer</t>
+          <t>Foster</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30348</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>45659</v>
+        <v>1</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>37829</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>45658</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
@@ -1236,12 +1224,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Caitlyn</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rodriguez</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1258,11 +1246,11 @@
       <c r="G20" t="b">
         <v>1</v>
       </c>
-      <c r="H20" s="2" t="n">
-        <v>29915</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>45660</v>
+      <c r="H20" s="1" t="n">
+        <v>29927</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>45658</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
@@ -1277,17 +1265,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mcguire</t>
+          <t>Mcmahon</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1299,11 +1287,11 @@
       <c r="G21" t="b">
         <v>0</v>
       </c>
-      <c r="H21" s="2" t="n">
-        <v>31701</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>45658</v>
+      <c r="H21" s="1" t="n">
+        <v>31920</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>45661</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
@@ -1318,12 +1306,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Montgomery</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1340,221 +1328,16 @@
       <c r="G22" t="b">
         <v>1</v>
       </c>
-      <c r="H22" s="2" t="n">
-        <v>28961</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>45661</v>
+      <c r="H22" s="1" t="n">
+        <v>37206</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>45659</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>L15</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>77</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Kimberly</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Holland</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="E23" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30570</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>45293</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>L14</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>78</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Micheal</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Oconnell</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E24" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" t="b">
-        <v>1</v>
-      </c>
-      <c r="G24" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>35027</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>45293</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>L14</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>79</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Charles</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Gonzalez</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E25" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>27748</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>45293</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>L14</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>80</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Joshua</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Mcdonald</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E26" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30530</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>45293</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>L14</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>81</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Jennifer</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Sanders</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E27" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>33118</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>45293</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>L14</t>
         </is>
       </c>
     </row>

--- a/data_new/newEmployees.xlsx
+++ b/data_new/newEmployees.xlsx
@@ -509,7 +509,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>37096</v>
+        <v>37099</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>44564</v>
@@ -550,7 +550,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>38155</v>
+        <v>38158</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>44563</v>
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>34984</v>
+        <v>34987</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>44564</v>
@@ -632,7 +632,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>30944</v>
+        <v>30947</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>44562</v>
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>38024</v>
+        <v>38027</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>44564</v>
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>35659</v>
+        <v>35662</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>44930</v>
@@ -755,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>31145</v>
+        <v>31148</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>44930</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>31440</v>
+        <v>31443</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>44930</v>
@@ -837,7 +837,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>29458</v>
+        <v>29461</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>44928</v>
@@ -878,7 +878,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>34252</v>
+        <v>34255</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>44927</v>
@@ -919,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>37119</v>
+        <v>37122</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>45294</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>35404</v>
+        <v>35407</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>45293</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>29629</v>
+        <v>29632</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>45295</v>
@@ -1042,7 +1042,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>36954</v>
+        <v>36957</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>45294</v>
@@ -1083,7 +1083,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>38208</v>
+        <v>38211</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>45292</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>29299</v>
+        <v>29302</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>45660</v>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>35791</v>
+        <v>35794</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>45660</v>
@@ -1206,7 +1206,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>37829</v>
+        <v>37832</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>45658</v>
@@ -1247,7 +1247,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>29927</v>
+        <v>29930</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>45658</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>31920</v>
+        <v>31923</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>45661</v>
@@ -1329,7 +1329,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>37206</v>
+        <v>37209</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>45659</v>
